--- a/virtual-physics-lab/app/dl/EJC_Q1_parametric.xlsx
+++ b/virtual-physics-lab/app/dl/EJC_Q1_parametric.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,41 +551,41 @@
       <c r="A6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>13.63</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>13.71</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>15.73</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>15.77</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>30.1</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -685,40 +689,40 @@
       <c r="A6" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>13.63</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>13.71</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="F6" s="7">
-        <f>(B6+C6)/40</f>
+      <c r="F6" s="8">
+        <f>ROUND((B6+C6)/40,3)</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>9.81*F6^2/PI()^2</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>E6^2/A6^2</f>
         <v/>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>% difference in k</t>
         </is>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="8">
         <f>ABS(H6-H7)/MIN(H6:H7)*100</f>
         <v/>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -728,40 +732,40 @@
       <c r="A7" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>15.73</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>15.77</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>30.1</v>
       </c>
-      <c r="F7" s="7">
-        <f>(B7+C7)/40</f>
+      <c r="F7" s="8">
+        <f>ROUND((B7+C7)/40,3)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <f>9.81*F7^2/PI()^2</f>
         <v/>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <f>E7^2/A7^2</f>
         <v/>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>2 × % uncertainty in t (Δt = 1 s)</t>
         </is>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="8">
         <f>2*1/E6*100</f>
         <v/>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
